--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487148_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487148_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.041399999999999</v>
+        <v>6.7098</v>
       </c>
       <c r="E2" t="n">
-        <v>8.3866</v>
+        <v>7.8046</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.3452</v>
+        <v>-1.0948</v>
       </c>
       <c r="G2" t="n">
         <v>2.8753</v>
@@ -610,13 +610,13 @@
         <v>2.3161</v>
       </c>
       <c r="S2" t="n">
-        <v>2.3227</v>
+        <v>0.9911</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3662</v>
+        <v>-0.2158</v>
       </c>
       <c r="U2" t="n">
-        <v>1.9565</v>
+        <v>1.2069</v>
       </c>
       <c r="V2" t="n">
         <v>1.6854</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>F. RODRIGUEZ HERRON</t>
+          <t>L. BLANCO DE LA CRUZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.046</v>
+        <v>-0.2136</v>
       </c>
       <c r="E3" t="n">
-        <v>2.2616</v>
+        <v>0.5212</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.2156</v>
+        <v>-0.7348</v>
       </c>
       <c r="G3" t="n">
-        <v>1.7947</v>
+        <v>-1.5628</v>
       </c>
       <c r="H3" t="n">
-        <v>2.755</v>
+        <v>0.3043</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.9604</v>
+        <v>-1.8672</v>
       </c>
       <c r="J3" t="n">
-        <v>2.9755</v>
+        <v>0.9462</v>
       </c>
       <c r="K3" t="n">
-        <v>2.9755</v>
+        <v>1.5731</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>-0.6269</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.1808</v>
+        <v>-2.5091</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.2204</v>
+        <v>-1.2688</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.9604</v>
+        <v>-1.2403</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.386</v>
+        <v>1.3511</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.965</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.579</v>
+        <v>1.3511</v>
       </c>
       <c r="S3" t="n">
-        <v>1.0933</v>
+        <v>-0.0674</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2512</v>
+        <v>-0.425</v>
       </c>
       <c r="U3" t="n">
-        <v>0.8421</v>
+        <v>0.3576</v>
       </c>
       <c r="V3" t="n">
-        <v>-2.4559</v>
+        <v>0.06560000000000001</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.4559</v>
+        <v>0.06560000000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>L. BLANCO DE LA CRUZ</t>
+          <t>L. SANCHEZ TURRION</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.4475</v>
+        <v>-0.5061</v>
       </c>
       <c r="E4" t="n">
-        <v>0.662</v>
+        <v>0.0226</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.1096</v>
+        <v>-0.5286999999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.5628</v>
+        <v>-0.2648</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3043</v>
+        <v>-0.1656</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.8672</v>
+        <v>-0.0993</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9462</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>1.5731</v>
+        <v>0.0414</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.6269</v>
+        <v>0.0407</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.5091</v>
+        <v>-0.3469</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.2688</v>
+        <v>-0.207</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.2403</v>
+        <v>-0.14</v>
       </c>
       <c r="P4" t="n">
-        <v>1.3511</v>
+        <v>0.193</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3511</v>
+        <v>0.193</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3014</v>
+        <v>-0.1484</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2842</v>
+        <v>-0.0595</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0172</v>
+        <v>-0.08890000000000001</v>
       </c>
       <c r="V4" t="n">
-        <v>0.06560000000000001</v>
+        <v>-0.2859</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0.06560000000000001</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>L. SANCHEZ TURRION</t>
+          <t>F. RODRIGUEZ HERRON</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.5329</v>
+        <v>-0.5757</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0226</v>
+        <v>1.9612</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.5555</v>
+        <v>-2.5368</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.2648</v>
+        <v>1.7947</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.1656</v>
+        <v>2.755</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0993</v>
+        <v>-0.9604</v>
       </c>
       <c r="J5" t="n">
-        <v>0.08210000000000001</v>
+        <v>2.9755</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0414</v>
+        <v>2.9755</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0407</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.3469</v>
+        <v>-1.1808</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.207</v>
+        <v>-0.2204</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.14</v>
+        <v>-0.9604</v>
       </c>
       <c r="P5" t="n">
-        <v>0.193</v>
+        <v>-0.386</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.965</v>
       </c>
       <c r="R5" t="n">
-        <v>0.193</v>
+        <v>0.579</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1752</v>
+        <v>0.4716</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0595</v>
+        <v>-0.0492</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1157</v>
+        <v>0.5208</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.2859</v>
+        <v>-2.4559</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2859</v>
+        <v>-2.4559</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>F. KONE FEZING</t>
+          <t>M. HERRERO CRESPO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.2033</v>
+        <v>-1.141</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.3646</v>
+        <v>-1.834</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.8387</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.3298</v>
+        <v>-2.9137</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5029</v>
+        <v>-0.8766</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.8268</v>
+        <v>-2.0371</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1449</v>
+        <v>-0.211</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1449</v>
+        <v>0.5794</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>-0.7904</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.4747</v>
+        <v>-2.7027</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6478</v>
+        <v>-1.456</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.8268</v>
+        <v>-1.2467</v>
       </c>
       <c r="P6" t="n">
-        <v>0.386</v>
+        <v>-1.9301</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-4.0532</v>
       </c>
       <c r="R6" t="n">
-        <v>0.386</v>
+        <v>2.1231</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2485</v>
+        <v>0.4191</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1468</v>
+        <v>-0.3116</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1018</v>
+        <v>0.7307</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.5081</v>
+        <v>3.2837</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.6562</v>
+        <v>2.7418</v>
       </c>
       <c r="X6" t="n">
-        <v>0.1481</v>
+        <v>0.5419</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. HERRERO CRESPO</t>
+          <t>F. KONE FEZING</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.6943</v>
+        <v>-1.4968</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.2534</v>
+        <v>-0.7651</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5591</v>
+        <v>-0.7316</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.9137</v>
+        <v>-1.3298</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.8766</v>
+        <v>-0.5029</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.0371</v>
+        <v>-0.8268</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.211</v>
+        <v>0.1449</v>
       </c>
       <c r="K7" t="n">
-        <v>0.5794</v>
+        <v>0.1449</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.7904</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.7027</v>
+        <v>-1.4747</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.456</v>
+        <v>-0.6478</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.2467</v>
+        <v>-0.8268</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.9301</v>
+        <v>0.386</v>
       </c>
       <c r="Q7" t="n">
-        <v>-4.0532</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.1231</v>
+        <v>0.386</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1342</v>
+        <v>-0.0449</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.731</v>
+        <v>-0.2538</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5968</v>
+        <v>0.2089</v>
       </c>
       <c r="V7" t="n">
-        <v>3.2837</v>
+        <v>-0.5081</v>
       </c>
       <c r="W7" t="n">
-        <v>2.7418</v>
+        <v>-0.6562</v>
       </c>
       <c r="X7" t="n">
-        <v>0.5419</v>
+        <v>0.1481</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R. GONZALEZ RUIZ</t>
+          <t>P. FERNANDEZ MENDIGUCHIA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.1255</v>
+        <v>-2.028</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.9236</v>
+        <v>-1.573</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.2018</v>
+        <v>-0.455</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.3271</v>
+        <v>0.5434</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.5195</v>
+        <v>-0.1242</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.8076</v>
+        <v>0.6676</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.6262</v>
+        <v>0.0828</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0414</v>
+        <v>0.0828</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6676</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.7009</v>
+        <v>0.4606</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.5609</v>
+        <v>-0.207</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.14</v>
+        <v>0.6676</v>
       </c>
       <c r="P8" t="n">
-        <v>0.193</v>
+        <v>-1.7371</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.9301</v>
       </c>
       <c r="R8" t="n">
         <v>0.193</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3774</v>
+        <v>0.3936</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2974</v>
+        <v>0.2743</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.08</v>
+        <v>0.1193</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.614</v>
+        <v>-1.228</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.614</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P. FERNANDEZ MENDIGUCHIA</t>
+          <t>R. GONZALEZ RUIZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.2015</v>
+        <v>-2.0452</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.7733</v>
+        <v>-0.9236</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4283</v>
+        <v>-1.1215</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5434</v>
+        <v>-1.3271</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1242</v>
+        <v>-0.5195</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6676</v>
+        <v>-0.8076</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0828</v>
+        <v>-0.6262</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0828</v>
+        <v>0.0414</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>-0.6676</v>
       </c>
       <c r="M9" t="n">
-        <v>0.4606</v>
+        <v>-0.7009</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.207</v>
+        <v>-0.5609</v>
       </c>
       <c r="O9" t="n">
-        <v>0.6676</v>
+        <v>-0.14</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.7371</v>
+        <v>0.193</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.9301</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>0.193</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2201</v>
+        <v>-0.2971</v>
       </c>
       <c r="T9" t="n">
-        <v>0.074</v>
+        <v>-0.2974</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1461</v>
+        <v>0.0003</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.228</v>
+        <v>-0.614</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.228</v>
+        <v>-0.614</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.3974</v>
+        <v>-2.7232</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.1262</v>
+        <v>-1.6661</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.2713</v>
+        <v>-1.0571</v>
       </c>
       <c r="G10" t="n">
         <v>-0.9569</v>
@@ -1234,13 +1234,13 @@
         <v>0.965</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7337</v>
+        <v>-0.0595</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7588</v>
+        <v>-0.2987</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0251</v>
+        <v>0.2393</v>
       </c>
       <c r="V10" t="n">
         <v>-1.5138</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.461</v>
+        <v>-3.6073</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.406</v>
+        <v>-2.6862</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.055</v>
+        <v>-0.9211</v>
       </c>
       <c r="G11" t="n">
         <v>-1.7524</v>
@@ -1312,13 +1312,13 @@
         <v>1.3511</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5942</v>
+        <v>0.2594</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8632</v>
+        <v>-0.1434</v>
       </c>
       <c r="U11" t="n">
-        <v>0.269</v>
+        <v>0.4028</v>
       </c>
       <c r="V11" t="n">
         <v>-1.3423</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.1162</v>
+        <v>-4.8703</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.079</v>
+        <v>-2.8598</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.0372</v>
+        <v>-2.0104</v>
       </c>
       <c r="G12" t="n">
         <v>-3.779</v>
@@ -1390,13 +1390,13 @@
         <v>1.9301</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.4581</v>
+        <v>-0.2122</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6861</v>
+        <v>-0.467</v>
       </c>
       <c r="U12" t="n">
-        <v>0.228</v>
+        <v>0.2548</v>
       </c>
       <c r="V12" t="n">
         <v>-0.6861</v>
@@ -1423,16 +1423,16 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-13.0922</v>
+        <v>-12.4974</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.593300000000001</v>
+        <v>-1.9982</v>
       </c>
       <c r="F13" t="n">
-        <v>-10.4991</v>
+        <v>-10.4988</v>
       </c>
       <c r="G13" t="n">
-        <v>-8.6731</v>
+        <v>-8.673099999999998</v>
       </c>
       <c r="H13" t="n">
         <v>0.8017000000000001</v>
@@ -1441,7 +1441,7 @@
         <v>-9.475200000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>6.274799999999997</v>
+        <v>6.274799999999999</v>
       </c>
       <c r="K13" t="n">
         <v>8.816599999999999</v>
@@ -1468,13 +1468,13 @@
         <v>11.5805</v>
       </c>
       <c r="S13" t="n">
-        <v>1.1104</v>
+        <v>1.7053</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.842</v>
+        <v>-2.2471</v>
       </c>
       <c r="U13" t="n">
-        <v>3.952500000000001</v>
+        <v>3.9525</v>
       </c>
       <c r="V13" t="n">
         <v>-3.599400000000001</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.3807</v>
+        <v>8.4162</v>
       </c>
       <c r="E14" t="n">
-        <v>6.1642</v>
+        <v>6.6649</v>
       </c>
       <c r="F14" t="n">
-        <v>1.2165</v>
+        <v>1.7512</v>
       </c>
       <c r="G14" t="n">
         <v>7.5921</v>
@@ -1546,13 +1546,13 @@
         <v>2.3161</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.4396</v>
+        <v>-0.4042</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.3682</v>
+        <v>-0.8675</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.07140000000000001</v>
+        <v>0.4633</v>
       </c>
       <c r="V14" t="n">
         <v>-0.1228</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.9257</v>
+        <v>4.6673</v>
       </c>
       <c r="E15" t="n">
-        <v>2.7201</v>
+        <v>3.2208</v>
       </c>
       <c r="F15" t="n">
-        <v>1.2056</v>
+        <v>1.4465</v>
       </c>
       <c r="G15" t="n">
         <v>3.701</v>
@@ -1624,13 +1624,13 @@
         <v>1.158</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5823</v>
+        <v>0.1593</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.1303</v>
+        <v>-0.6296</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5479000000000001</v>
+        <v>0.7889</v>
       </c>
       <c r="V15" t="n">
         <v>0.614</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.486</v>
+        <v>4.0535</v>
       </c>
       <c r="E16" t="n">
-        <v>2.3783</v>
+        <v>2.6788</v>
       </c>
       <c r="F16" t="n">
-        <v>1.1077</v>
+        <v>1.3747</v>
       </c>
       <c r="G16" t="n">
         <v>0.9929</v>
@@ -1702,13 +1702,13 @@
         <v>1.9301</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6518</v>
+        <v>-0.0843</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.8923</v>
+        <v>-0.5919</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2406</v>
+        <v>0.5076000000000001</v>
       </c>
       <c r="V16" t="n">
         <v>5.0749</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.4461</v>
+        <v>2.5379</v>
       </c>
       <c r="E17" t="n">
-        <v>3.9961</v>
+        <v>3.195</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.55</v>
+        <v>-0.6571</v>
       </c>
       <c r="G17" t="n">
         <v>3.0939</v>
@@ -1780,13 +1780,13 @@
         <v>1.158</v>
       </c>
       <c r="S17" t="n">
-        <v>1.1012</v>
+        <v>0.193</v>
       </c>
       <c r="T17" t="n">
-        <v>0.6214</v>
+        <v>-0.1798</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4799</v>
+        <v>0.3728</v>
       </c>
       <c r="V17" t="n">
         <v>-0.9421</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. TOURE</t>
+          <t>D. CARRETERO GARCIA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.7433</v>
+        <v>1.1849</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6594</v>
+        <v>0.1625</v>
       </c>
       <c r="F18" t="n">
-        <v>1.0839</v>
+        <v>1.0223</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.0151</v>
+        <v>1.1547</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.7512</v>
+        <v>1.1789</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7361</v>
+        <v>-0.0243</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.1672</v>
+        <v>0.6136</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.2486</v>
+        <v>1.1592</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0814</v>
+        <v>-0.5455</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.8479</v>
+        <v>0.541</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.5026</v>
+        <v>0.0198</v>
       </c>
       <c r="O18" t="n">
-        <v>0.6546999999999999</v>
+        <v>0.5212</v>
       </c>
       <c r="P18" t="n">
-        <v>-2.3161</v>
+        <v>0.965</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.8602</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5441</v>
+        <v>0.965</v>
       </c>
       <c r="S18" t="n">
-        <v>2.4133</v>
+        <v>0.2931</v>
       </c>
       <c r="T18" t="n">
-        <v>1.6591</v>
+        <v>-0.4511</v>
       </c>
       <c r="U18" t="n">
-        <v>0.7542</v>
+        <v>0.7442</v>
       </c>
       <c r="V18" t="n">
-        <v>2.6613</v>
+        <v>-1.228</v>
       </c>
       <c r="W18" t="n">
-        <v>3.0277</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.3664</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. CARRETERO GARCIA</t>
+          <t>A. TOURE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5507</v>
+        <v>0.1874</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.3382</v>
+        <v>-0.8427</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8888</v>
+        <v>1.03</v>
       </c>
       <c r="G19" t="n">
-        <v>1.1547</v>
+        <v>-1.0151</v>
       </c>
       <c r="H19" t="n">
-        <v>1.1789</v>
+        <v>-1.7512</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.0243</v>
+        <v>0.7361</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6136</v>
+        <v>-0.1672</v>
       </c>
       <c r="K19" t="n">
-        <v>1.1592</v>
+        <v>-0.2486</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.5455</v>
+        <v>0.0814</v>
       </c>
       <c r="M19" t="n">
-        <v>0.541</v>
+        <v>-0.8479</v>
       </c>
       <c r="N19" t="n">
-        <v>0.0198</v>
+        <v>-1.5026</v>
       </c>
       <c r="O19" t="n">
-        <v>0.5212</v>
+        <v>0.6546999999999999</v>
       </c>
       <c r="P19" t="n">
-        <v>0.965</v>
+        <v>-2.3161</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-3.8602</v>
       </c>
       <c r="R19" t="n">
-        <v>0.965</v>
+        <v>1.5441</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3411</v>
+        <v>0.8573</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.9518</v>
+        <v>0.157</v>
       </c>
       <c r="U19" t="n">
-        <v>0.6107</v>
+        <v>0.7003</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.228</v>
+        <v>2.6613</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>3.0277</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.228</v>
+        <v>-0.3664</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.7278</v>
+        <v>-0.1266</v>
       </c>
       <c r="E20" t="n">
-        <v>0.947</v>
+        <v>1.1473</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.6748</v>
+        <v>-1.274</v>
       </c>
       <c r="G20" t="n">
         <v>-0.08450000000000001</v>
@@ -2014,13 +2014,13 @@
         <v>0.965</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.1574</v>
+        <v>-0.5562</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4759</v>
+        <v>-0.2756</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.6815</v>
+        <v>-0.2806</v>
       </c>
       <c r="V20" t="n">
         <v>-0.4509</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.7803</v>
+        <v>-0.5533</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.506</v>
+        <v>-0.3057</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.2743</v>
+        <v>-0.2476</v>
       </c>
       <c r="G21" t="n">
         <v>-1.0636</v>
@@ -2092,13 +2092,13 @@
         <v>0.965</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3536</v>
+        <v>-0.1266</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5354</v>
+        <v>-0.3351</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1818</v>
+        <v>0.2085</v>
       </c>
       <c r="V21" t="n">
         <v>-0.3281</v>
@@ -2125,10 +2125,10 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.8746</v>
+        <v>-0.7745</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.6676</v>
+        <v>-0.5675</v>
       </c>
       <c r="F22" t="n">
         <v>-0.207</v>
@@ -2170,10 +2170,10 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1335</v>
+        <v>-0.0334</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>0.1001</v>
       </c>
       <c r="U22" t="n">
         <v>-0.1335</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.6225</v>
+        <v>-3.7303</v>
       </c>
       <c r="E24" t="n">
         <v>-4.8544</v>
       </c>
       <c r="F24" t="n">
-        <v>1.2318</v>
+        <v>1.1241</v>
       </c>
       <c r="G24" t="n">
         <v>-4.8835</v>
@@ -2326,13 +2326,13 @@
         <v>2.5091</v>
       </c>
       <c r="S24" t="n">
-        <v>0.1679</v>
+        <v>0.0601</v>
       </c>
       <c r="T24" t="n">
         <v>-0.8791</v>
       </c>
       <c r="U24" t="n">
-        <v>1.0469</v>
+        <v>0.9392</v>
       </c>
       <c r="V24" t="n">
         <v>-0.4509</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>13.0923</v>
+        <v>14.4275</v>
       </c>
       <c r="E25" t="n">
-        <v>10.4989</v>
+        <v>10.499</v>
       </c>
       <c r="F25" t="n">
-        <v>2.5932</v>
+        <v>3.9281</v>
       </c>
       <c r="G25" t="n">
         <v>8.673300000000003</v>
@@ -2404,13 +2404,13 @@
         <v>13.5104</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.1104</v>
+        <v>0.2245999999999998</v>
       </c>
       <c r="T25" t="n">
-        <v>-3.9525</v>
+        <v>-3.9526</v>
       </c>
       <c r="U25" t="n">
-        <v>2.8421</v>
+        <v>4.177199999999999</v>
       </c>
       <c r="V25" t="n">
         <v>3.599400000000001</v>
